--- a/output/pdf_financials_xlsx/TKO.xlsx
+++ b/output/pdf_financials_xlsx/TKO.xlsx
@@ -6295,7 +6295,7 @@
         <v>52.845</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>52.845</v>
+        <v>90.271</v>
       </c>
     </row>
     <row r="92">
@@ -16136,7 +16136,11 @@
           <t>Foreign currency translation reserve (31,131)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -91640,7 +91644,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E795" s="5" t="n">

--- a/output/pdf_financials_xlsx/TKO.xlsx
+++ b/output/pdf_financials_xlsx/TKO.xlsx
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>172.732</v>
       </c>
     </row>
     <row r="35">
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>172.732</v>
       </c>
     </row>
     <row r="37">
@@ -3412,7 +3412,7 @@
         <v>208.706</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>208.706</v>
+        <v>35.974</v>
       </c>
     </row>
     <row r="49">
@@ -8252,10 +8252,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-1.061</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-3.199</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>-56.823</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-1.061</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-3.199</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>-56.823</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31746,7 +31746,11 @@
           <t>Reclamation deposits (note 17)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -34808,7 +34812,11 @@
           <t>Reclamation deposits (note 15)</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -50252,7 +50260,11 @@
           <t>Distribution of reclamation deposits 13</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -63452,7 +63464,11 @@
           <t>Accrued interest income on reclamation deposits</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E525" s="5" t="n">
         <v>-1.791</v>
       </c>
@@ -63552,7 +63568,11 @@
           <t>Funds released from reclamation deposits</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>-</t>
@@ -64278,7 +64298,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E533" s="5" t="n">
         <v>-0.02</v>
       </c>
@@ -64380,7 +64404,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -71398,7 +71426,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -73074,7 +73102,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -89154,7 +89182,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -90914,7 +90942,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -91644,7 +91672,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E795" s="5" t="n">
@@ -92784,7 +92812,7 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E806" s="5" t="n">

--- a/output/pdf_financials_xlsx/TKO.xlsx
+++ b/output/pdf_financials_xlsx/TKO.xlsx
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>18.665</v>
       </c>
       <c r="S9" s="1" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>49.894</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>18.665</v>
       </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>475.078</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>608.093</v>
+        <v>589.428</v>
       </c>
       <c r="S11" s="1" t="inlineStr">
         <is>
@@ -66772,7 +66772,11 @@
           <t>Other operating costs 5</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -66854,7 +66858,7 @@
         </is>
       </c>
       <c r="U557" s="5" t="n">
-        <v>-18.665</v>
+        <v>18.665</v>
       </c>
       <c r="V557" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TKO.xlsx
+++ b/output/pdf_financials_xlsx/TKO.xlsx
@@ -1405,16 +1405,16 @@
         <v>23.782</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5.735</v>
+        <v>0.584</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.461</v>
+        <v>2.659</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>21.693</v>
+        <v>-8.787000000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.68</v>
+        <v>-5.605</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-14.713</v>
@@ -2359,16 +2359,16 @@
         <v>46.85554417211758</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-67.03682057276447</v>
+        <v>-6.826417299824664</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-1.432566811684276</v>
+        <v>-8.262896208825357</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-34.61409583379872</v>
+        <v>-14.0208389845383</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-1.000632753064438</v>
+        <v>-8.247862619009078</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-31.90917174521243</v>
@@ -2869,46 +2869,46 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>12.961</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.336</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>2.292</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>3.237</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>1.409</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>2.646</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>1.822</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>1.418</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="41">
@@ -2932,46 +2932,46 @@
         <v>12.505</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>39.909</v>
+        <v>41.309</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>52.87</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>4.532</v>
+        <v>5.637</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>12.618</v>
+        <v>12.954</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>13.199</v>
+        <v>13.538</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>12.905</v>
+        <v>15.197</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>21.618</v>
+        <v>22.591</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>14.735</v>
+        <v>17.972</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>13.791</v>
+        <v>15.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>9.603999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>13.223</v>
+        <v>15.045</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>16.514</v>
+        <v>17.932</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>5.643</v>
+        <v>5.889</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>5.643</v>
+        <v>5.872</v>
       </c>
     </row>
     <row r="42">
@@ -3373,46 +3373,46 @@
         <v>58.828</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>373.724</v>
+        <v>372.324</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>360.763</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>177.232</v>
+        <v>176.127</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>87.919</v>
+        <v>87.583</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>71.73999999999999</v>
+        <v>71.401</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>91.872</v>
+        <v>89.58</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>84.479</v>
+        <v>83.506</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>50.71</v>
+        <v>47.473</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>56.441</v>
+        <v>55.032</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>247.752</v>
+        <v>245.106</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>134.802</v>
+        <v>132.98</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>109.999</v>
+        <v>108.581</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>208.706</v>
+        <v>208.46</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>35.974</v>
+        <v>35.745</v>
       </c>
     </row>
     <row r="49">
@@ -4483,46 +4483,46 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>31.055</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>39.963</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>22.768</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>36.873</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>26.293</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>28.18</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>23.926</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>21.861</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>24.171</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>31.719</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>71.748</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>129.927</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>100.273</v>
       </c>
     </row>
     <row r="65">
@@ -4687,31 +4687,31 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>4.012</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>18.692</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>19.14</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>19.514</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>25.56</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>34.997</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>43.191</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>64.586</v>
       </c>
     </row>
     <row r="68">
@@ -4750,19 +4750,19 @@
         <v>30.143</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>32.192</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>42.618</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>41.001</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>43.685</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>55.66</v>
       </c>
       <c r="P68" s="3" t="n">
         <v>66.71599999999999</v>
@@ -5191,19 +5191,19 @@
         <v>5.507</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>38.641</v>
+        <v>6.449</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>10.499</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>8.211</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>39.816</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>15.448</v>
@@ -7230,19 +7230,19 @@
         <v>5.423</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>3.741</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>2.002</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>3.682</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M107" s="3" t="n">
         <v>0</v>
@@ -7251,19 +7251,19 @@
         <v>0</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>5.762</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>-1.2</v>
+        <v>2.952</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>-0.385</v>
+        <v>5.941</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>2.632</v>
+        <v>9.425000000000001</v>
       </c>
       <c r="S107" s="3" t="n">
-        <v>0</v>
+        <v>21.971</v>
       </c>
     </row>
     <row r="108">
@@ -7440,13 +7440,13 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>10.759</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>46.937</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>60.442</v>
       </c>
     </row>
     <row r="111">
@@ -7700,16 +7700,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>16.999</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>9.965999999999999</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>16.449</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-20.897</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -8568,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="O128" s="3" t="n">
-        <v>0</v>
+        <v>-1.451</v>
       </c>
       <c r="P128" s="3" t="n">
         <v>0</v>
@@ -37870,7 +37870,11 @@
           <t>Accretion expense 7</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -38818,7 +38822,11 @@
           <t>Share-based compensation expense 23c</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -41122,7 +41130,11 @@
           <t>Net proceeds from share issuances 21</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -42272,7 +42284,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -43092,7 +43108,11 @@
           <t>Share-based compensation expense 22b</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -45792,7 +45812,11 @@
           <t>Share-based compensation expense 22c</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -48076,7 +48100,11 @@
           <t>Share-based compensation expense 21c</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -49122,7 +49150,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -52234,7 +52266,11 @@
           <t>Share-based compensation expense 22</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -53288,7 +53324,11 @@
           <t>Share-based compensation expense 21</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -54750,7 +54790,11 @@
           <t>Share-based compensation expense 20</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -55992,7 +56036,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -56510,7 +56558,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -57738,7 +57790,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -60774,7 +60830,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E499" s="5" t="n">
         <v>35.645</v>
       </c>
@@ -64198,7 +64258,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E532" s="5" t="n">
         <v>16.999</v>
       </c>
@@ -79688,7 +79752,11 @@
           <t>Income tax recovery 10</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E681" t="inlineStr">
         <is>
           <t>-</t>
@@ -81912,7 +81980,11 @@
           <t>Income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E702" t="inlineStr">
         <is>
           <t>-</t>
@@ -83722,7 +83794,11 @@
           <t>Income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E719" t="inlineStr">
         <is>
           <t>-</t>
@@ -85850,7 +85926,11 @@
           <t>Income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E739" t="inlineStr">
         <is>
           <t>-</t>
@@ -88132,7 +88212,11 @@
           <t>Income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E761" t="inlineStr">
         <is>
           <t>-</t>
